--- a/exports/trend_1d/ADANIPORTS_full_report.xlsx
+++ b/exports/trend_1d/ADANIPORTS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42039</v>
+        <v>42040</v>
       </c>
       <c r="H2" t="n">
-        <v>321.25</v>
+        <v>312.2</v>
       </c>
       <c r="I2" t="n">
         <v>313.4004423334899</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.83</v>
+        <v>-5.57</v>
       </c>
       <c r="L2" t="n">
-        <v>3.43</v>
+        <v>6.7</v>
       </c>
       <c r="M2" t="n">
         <v>0.51</v>
       </c>
       <c r="N2" t="n">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="O2" t="n">
         <v>-0.2</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>13.35</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42061</v>
+        <v>42062</v>
       </c>
       <c r="H3" t="n">
-        <v>327.3</v>
+        <v>346.25</v>
       </c>
       <c r="I3" t="n">
         <v>339.978323645718</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.84</v>
+        <v>-10.91</v>
       </c>
       <c r="L3" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0.64</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>14.01</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42153</v>
+        <v>42156</v>
       </c>
       <c r="H4" t="n">
-        <v>323.85</v>
+        <v>311.55</v>
       </c>
       <c r="I4" t="n">
         <v>317.8763847635927</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.47</v>
+        <v>-10.02</v>
       </c>
       <c r="L4" t="n">
         <v>14.69</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>13.35</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42219</v>
+        <v>42220</v>
       </c>
       <c r="H5" t="n">
-        <v>330.7</v>
+        <v>339.15</v>
       </c>
       <c r="I5" t="n">
         <v>333.9487490688438</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.15</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>7.43</v>
+        <v>9.23</v>
       </c>
       <c r="M5" t="n">
         <v>2.25</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42251</v>
+        <v>42254</v>
       </c>
       <c r="H6" t="n">
-        <v>339.35</v>
+        <v>322.64</v>
       </c>
       <c r="I6" t="n">
         <v>331.8624687227345</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06</v>
+        <v>-4.87</v>
       </c>
       <c r="L6" t="n">
         <v>5.54</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>18.7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42369</v>
+        <v>42370</v>
       </c>
       <c r="H7" t="n">
-        <v>260.9</v>
+        <v>267.55</v>
       </c>
       <c r="I7" t="n">
         <v>265.3392020322154</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K7" t="n">
-        <v>19.14</v>
+        <v>17.07</v>
       </c>
       <c r="L7" t="n">
         <v>8.85</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,25 +971,25 @@
         <v>8.16</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42375</v>
+        <v>42376</v>
       </c>
       <c r="H8" t="n">
-        <v>251.8</v>
+        <v>245</v>
       </c>
       <c r="I8" t="n">
         <v>245.7133922584771</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.89</v>
+        <v>-8.43</v>
       </c>
       <c r="L8" t="n">
-        <v>6.35</v>
+        <v>9.74</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16</v>
+        <v>2.44</v>
       </c>
       <c r="N8" t="n">
         <v>3.59</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42430</v>
+        <v>42431</v>
       </c>
       <c r="H9" t="n">
-        <v>206.9</v>
+        <v>218.8</v>
       </c>
       <c r="I9" t="n">
         <v>214.2405646876864</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" t="n">
-        <v>15.55</v>
+        <v>10.69</v>
       </c>
       <c r="L9" t="n">
         <v>1.02</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.47</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42466</v>
+        <v>42467</v>
       </c>
       <c r="H10" t="n">
-        <v>224.35</v>
+        <v>216.8</v>
       </c>
       <c r="I10" t="n">
         <v>220.4024891194969</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K10" t="n">
-        <v>2.54</v>
+        <v>-0.91</v>
       </c>
       <c r="L10" t="n">
         <v>4.55</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>15.87</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42522</v>
+        <v>42523</v>
       </c>
       <c r="H11" t="n">
-        <v>202.3</v>
+        <v>205.2</v>
       </c>
       <c r="I11" t="n">
         <v>203.7058219749969</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>6.69</v>
+        <v>5.35</v>
       </c>
       <c r="L11" t="n">
         <v>11.83</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.47</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42653</v>
+        <v>42656</v>
       </c>
       <c r="H12" t="n">
-        <v>264</v>
+        <v>251.1</v>
       </c>
       <c r="I12" t="n">
         <v>251.3778226909934</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K12" t="n">
-        <v>28.65</v>
+        <v>22.37</v>
       </c>
       <c r="L12" t="n">
         <v>4.8</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.52</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42662</v>
+        <v>42663</v>
       </c>
       <c r="H13" t="n">
-        <v>271.6</v>
+        <v>285.25</v>
       </c>
       <c r="I13" t="n">
         <v>277.0394760414067</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.16</v>
+        <v>-13.6</v>
       </c>
       <c r="L13" t="n">
-        <v>8.880000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="M13" t="n">
         <v>0.75</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>13.46</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H14" t="n">
-        <v>276.75</v>
+        <v>266.65</v>
       </c>
       <c r="I14" t="n">
         <v>269.7116467779085</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.98</v>
+        <v>-6.52</v>
       </c>
       <c r="L14" t="n">
-        <v>8.539999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>7.54</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>17.59</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H15" t="n">
-        <v>274.9</v>
+        <v>287.5</v>
       </c>
       <c r="I15" t="n">
         <v>285.2172143034312</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.09</v>
+        <v>-7.82</v>
       </c>
       <c r="L15" t="n">
         <v>9.380000000000001</v>
@@ -1296,7 +1475,7 @@
         <v>2.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>4.58</v>
       </c>
       <c r="O15" t="n">
         <v>-3.65</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.47</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42836</v>
+        <v>42837</v>
       </c>
       <c r="H16" t="n">
-        <v>333.8</v>
+        <v>327.6</v>
       </c>
       <c r="I16" t="n">
         <v>328.6142054317997</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K16" t="n">
-        <v>16.1</v>
+        <v>13.95</v>
       </c>
       <c r="L16" t="n">
         <v>4.17</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>10.62</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42865</v>
+        <v>42866</v>
       </c>
       <c r="H17" t="n">
-        <v>351.9</v>
+        <v>360.05</v>
       </c>
       <c r="I17" t="n">
         <v>353.7670473345767</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.42</v>
+        <v>-9.91</v>
       </c>
       <c r="L17" t="n">
-        <v>7.75</v>
+        <v>10.67</v>
       </c>
       <c r="M17" t="n">
         <v>0.83</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H18" t="n">
-        <v>397.25</v>
+        <v>385.65</v>
       </c>
       <c r="I18" t="n">
         <v>390.5764962314017</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K18" t="n">
-        <v>10.33</v>
+        <v>7.11</v>
       </c>
       <c r="L18" t="n">
         <v>9.710000000000001</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43019</v>
+        <v>43020</v>
       </c>
       <c r="H19" t="n">
-        <v>396.95</v>
+        <v>403.7</v>
       </c>
       <c r="I19" t="n">
         <v>402.5512193507464</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.93</v>
+        <v>-4.68</v>
       </c>
       <c r="L19" t="n">
         <v>7.53</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43054</v>
+        <v>43055</v>
       </c>
       <c r="H20" t="n">
-        <v>407.1</v>
+        <v>397.2</v>
       </c>
       <c r="I20" t="n">
         <v>406.7771227969155</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>0.84</v>
+        <v>-1.61</v>
       </c>
       <c r="L20" t="n">
         <v>2.71</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>10.21</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43104</v>
+        <v>43105</v>
       </c>
       <c r="H21" t="n">
-        <v>409.85</v>
+        <v>423.8</v>
       </c>
       <c r="I21" t="n">
         <v>417.7393951382936</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.18</v>
+        <v>-6.7</v>
       </c>
       <c r="L21" t="n">
-        <v>4.9</v>
+        <v>7.49</v>
       </c>
       <c r="M21" t="n">
         <v>2.68</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43139</v>
+        <v>43140</v>
       </c>
       <c r="H22" t="n">
-        <v>405.1</v>
+        <v>399</v>
       </c>
       <c r="I22" t="n">
         <v>401.3890376999451</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.41</v>
+        <v>-5.85</v>
       </c>
       <c r="L22" t="n">
         <v>8.68</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.12</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43216</v>
+        <v>43217</v>
       </c>
       <c r="H23" t="n">
-        <v>397.1</v>
+        <v>402.45</v>
       </c>
       <c r="I23" t="n">
         <v>397.6336525840143</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
-        <v>0.48</v>
+        <v>-0.86</v>
       </c>
       <c r="L23" t="n">
         <v>6.27</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>7.72</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43238</v>
+        <v>43241</v>
       </c>
       <c r="H24" t="n">
-        <v>389.5</v>
+        <v>383.7</v>
       </c>
       <c r="I24" t="n">
         <v>385.5720705949137</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.22</v>
+        <v>-4.66</v>
       </c>
       <c r="L24" t="n">
-        <v>4.57</v>
+        <v>5.21</v>
       </c>
       <c r="M24" t="n">
         <v>2.67</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.68</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43304</v>
+        <v>43305</v>
       </c>
       <c r="H25" t="n">
-        <v>383.75</v>
+        <v>392.6</v>
       </c>
       <c r="I25" t="n">
         <v>387.9707773089548</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.01</v>
+        <v>-2.32</v>
       </c>
       <c r="L25" t="n">
         <v>3.62</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43326</v>
+        <v>43328</v>
       </c>
       <c r="H26" t="n">
-        <v>373.15</v>
+        <v>370.3</v>
       </c>
       <c r="I26" t="n">
         <v>371.130852963231</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.95</v>
+        <v>-5.68</v>
       </c>
       <c r="L26" t="n">
-        <v>5.96</v>
+        <v>6.44</v>
       </c>
       <c r="M26" t="n">
         <v>0.97</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.83</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43420</v>
+        <v>43423</v>
       </c>
       <c r="H27" t="n">
-        <v>347.45</v>
+        <v>350.55</v>
       </c>
       <c r="I27" t="n">
         <v>348.4543184119892</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K27" t="n">
-        <v>6.17</v>
+        <v>5.33</v>
       </c>
       <c r="L27" t="n">
         <v>6.4</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.57</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43490</v>
+        <v>43493</v>
       </c>
       <c r="H28" t="n">
-        <v>373.85</v>
+        <v>326.1</v>
       </c>
       <c r="I28" t="n">
         <v>370.5452591270823</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K28" t="n">
-        <v>6.65</v>
+        <v>-6.97</v>
       </c>
       <c r="L28" t="n">
-        <v>2.32</v>
+        <v>16.67</v>
       </c>
       <c r="M28" t="n">
         <v>3.57</v>
       </c>
       <c r="N28" t="n">
-        <v>3.83</v>
+        <v>12.77</v>
       </c>
       <c r="O28" t="n">
         <v>0.89</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.59</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43536</v>
+        <v>43537</v>
       </c>
       <c r="H29" t="n">
-        <v>361.05</v>
+        <v>367.15</v>
       </c>
       <c r="I29" t="n">
         <v>363.0593825449836</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K29" t="n">
-        <v>-10.72</v>
+        <v>-12.59</v>
       </c>
       <c r="L29" t="n">
         <v>15.1</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.3</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H30" t="n">
-        <v>369.8</v>
+        <v>363.9</v>
       </c>
       <c r="I30" t="n">
         <v>369.123733413441</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K30" t="n">
-        <v>0.72</v>
+        <v>-0.89</v>
       </c>
       <c r="L30" t="n">
         <v>3.81</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.02</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H31" t="n">
-        <v>367.1</v>
+        <v>400.1</v>
       </c>
       <c r="I31" t="n">
         <v>393.0800189066972</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.88</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>4.07</v>
+        <v>12.17</v>
       </c>
       <c r="M31" t="n">
-        <v>0.24</v>
+        <v>5.83</v>
       </c>
       <c r="N31" t="n">
-        <v>3.15</v>
+        <v>8.99</v>
       </c>
       <c r="O31" t="n">
         <v>-1.6</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.36</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H32" t="n">
-        <v>399.75</v>
+        <v>380.8</v>
       </c>
       <c r="I32" t="n">
         <v>395.2324822440823</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.09</v>
+        <v>-4.82</v>
       </c>
       <c r="L32" t="n">
         <v>6.01</v>
@@ -2265,7 +2648,7 @@
         <v>2.39</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>4.74</v>
       </c>
       <c r="O32" t="n">
         <v>8.99</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.38</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>361.9</v>
+        <v>380.7</v>
       </c>
       <c r="I33" t="n">
         <v>375.8664042391836</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K33" t="n">
-        <v>4.96</v>
+        <v>0.03</v>
       </c>
       <c r="L33" t="n">
         <v>5.19</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.81</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H34" t="n">
-        <v>390.45</v>
+        <v>386.15</v>
       </c>
       <c r="I34" t="n">
         <v>389.7339530483841</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K34" t="n">
-        <v>2.56</v>
+        <v>1.43</v>
       </c>
       <c r="L34" t="n">
         <v>5.17</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.66</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43838</v>
+        <v>43839</v>
       </c>
       <c r="H35" t="n">
-        <v>385.65</v>
+        <v>391.8</v>
       </c>
       <c r="I35" t="n">
         <v>388.9290065995098</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K35" t="n">
-        <v>0.13</v>
+        <v>-1.46</v>
       </c>
       <c r="L35" t="n">
-        <v>1.46</v>
+        <v>2.03</v>
       </c>
       <c r="M35" t="n">
         <v>2.01</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.05</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H36" t="n">
-        <v>378</v>
+        <v>369.4</v>
       </c>
       <c r="I36" t="n">
         <v>370.5816198274479</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.52</v>
+        <v>-5.72</v>
       </c>
       <c r="L36" t="n">
-        <v>5.51</v>
+        <v>6.01</v>
       </c>
       <c r="M36" t="n">
         <v>0.74</v>
       </c>
       <c r="N36" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="O36" t="n">
         <v>1.59</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43963</v>
+        <v>43964</v>
       </c>
       <c r="H37" t="n">
-        <v>291.5</v>
+        <v>309.35</v>
       </c>
       <c r="I37" t="n">
         <v>291.7089668282517</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K37" t="n">
-        <v>21.09</v>
+        <v>16.26</v>
       </c>
       <c r="L37" t="n">
         <v>3.29</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>22.84</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H38" t="n">
-        <v>332.2</v>
+        <v>320.4</v>
       </c>
       <c r="I38" t="n">
         <v>330.5988645595154</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K38" t="n">
-        <v>7.39</v>
+        <v>3.57</v>
       </c>
       <c r="L38" t="n">
         <v>15.19</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>11.8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44053</v>
+        <v>44054</v>
       </c>
       <c r="H39" t="n">
-        <v>331.3</v>
+        <v>335</v>
       </c>
       <c r="I39" t="n">
         <v>333.6090328961236</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.4</v>
+        <v>-4.56</v>
       </c>
       <c r="L39" t="n">
-        <v>4.23</v>
+        <v>5.1</v>
       </c>
       <c r="M39" t="n">
         <v>1.13</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>8.65</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44096</v>
+        <v>44097</v>
       </c>
       <c r="H40" t="n">
-        <v>332.3</v>
+        <v>324.6</v>
       </c>
       <c r="I40" t="n">
         <v>332.2815060929137</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.1</v>
       </c>
       <c r="L40" t="n">
-        <v>2.34</v>
+        <v>4.43</v>
       </c>
       <c r="M40" t="n">
         <v>0.71</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>13.09</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44109</v>
+        <v>44110</v>
       </c>
       <c r="H41" t="n">
-        <v>350.35</v>
+        <v>362.9</v>
       </c>
       <c r="I41" t="n">
         <v>356.6954974184816</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-7.93</v>
+        <v>-11.8</v>
       </c>
       <c r="L41" t="n">
-        <v>10.29</v>
+        <v>12.29</v>
       </c>
       <c r="M41" t="n">
         <v>1.67</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>11.86</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44358</v>
+        <v>44361</v>
       </c>
       <c r="H42" t="n">
-        <v>839.75</v>
+        <v>768.45</v>
       </c>
       <c r="I42" t="n">
         <v>783.24192467279</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K42" t="n">
-        <v>131.4</v>
+        <v>111.75</v>
       </c>
       <c r="L42" t="n">
         <v>5.99</v>
       </c>
       <c r="M42" t="n">
-        <v>5.36</v>
+        <v>10</v>
       </c>
       <c r="N42" t="n">
         <v>9.59</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>170</v>
+        <v>171</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>9</v>
+      </c>
+      <c r="U42" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H43" t="n">
-        <v>730</v>
+        <v>748.3</v>
       </c>
       <c r="I43" t="n">
         <v>731.7926730961324</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>2.62</v>
       </c>
       <c r="L43" t="n">
         <v>4.48</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H44" t="n">
-        <v>761.8</v>
+        <v>752.05</v>
       </c>
       <c r="I44" t="n">
         <v>753.476245083812</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K44" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="L44" t="n">
         <v>3.53</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>9.92</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44574</v>
+        <v>44575</v>
       </c>
       <c r="H45" t="n">
-        <v>772.2</v>
+        <v>780.1</v>
       </c>
       <c r="I45" t="n">
         <v>775.9580139383162</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.68</v>
+        <v>-3.73</v>
       </c>
       <c r="L45" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="M45" t="n">
         <v>1.73</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>8.17</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H46" t="n">
-        <v>723.9</v>
+        <v>702.45</v>
       </c>
       <c r="I46" t="n">
         <v>720.3379794681513</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.2</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>8.42</v>
+        <v>11.68</v>
       </c>
       <c r="M46" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="O46" t="n">
         <v>1.02</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44644</v>
+        <v>44645</v>
       </c>
       <c r="H47" t="n">
-        <v>733.45</v>
+        <v>743.25</v>
       </c>
       <c r="I47" t="n">
         <v>742.0360217770256</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.41</v>
+        <v>-5.81</v>
       </c>
       <c r="L47" t="n">
         <v>6.91</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H48" t="n">
-        <v>811.4</v>
+        <v>792.6</v>
       </c>
       <c r="I48" t="n">
         <v>804.8859849555296</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K48" t="n">
-        <v>9.17</v>
+        <v>6.64</v>
       </c>
       <c r="L48" t="n">
         <v>2.25</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.98</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44757</v>
+        <v>44760</v>
       </c>
       <c r="H49" t="n">
-        <v>730.9</v>
+        <v>739.75</v>
       </c>
       <c r="I49" t="n">
         <v>732.9869977312163</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K49" t="n">
-        <v>7.78</v>
+        <v>6.67</v>
       </c>
       <c r="L49" t="n">
         <v>1.87</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.15</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H50" t="n">
-        <v>913.8</v>
+        <v>863.4</v>
       </c>
       <c r="I50" t="n">
         <v>890.5459181885315</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K50" t="n">
-        <v>23.53</v>
+        <v>16.72</v>
       </c>
       <c r="L50" t="n">
         <v>0.97</v>
@@ -3291,7 +3890,7 @@
         <v>2.7</v>
       </c>
       <c r="N50" t="n">
-        <v>3.85</v>
+        <v>5.52</v>
       </c>
       <c r="O50" t="n">
         <v>1.21</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>14.34</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44872</v>
+        <v>44874</v>
       </c>
       <c r="H51" t="n">
-        <v>853</v>
+        <v>890.8</v>
       </c>
       <c r="I51" t="n">
         <v>867.8494627451455</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K51" t="n">
-        <v>1.2</v>
+        <v>-3.17</v>
       </c>
       <c r="L51" t="n">
         <v>5.39</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H52" t="n">
-        <v>856.9</v>
+        <v>794.1</v>
       </c>
       <c r="I52" t="n">
         <v>845.8187336522396</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.81</v>
+        <v>-10.86</v>
       </c>
       <c r="L52" t="n">
-        <v>5.08</v>
+        <v>11.29</v>
       </c>
       <c r="M52" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="N52" t="n">
-        <v>3.01</v>
+        <v>7.33</v>
       </c>
       <c r="O52" t="n">
         <v>4.43</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>14.47</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H53" t="n">
-        <v>622.9</v>
+        <v>684.65</v>
       </c>
       <c r="I53" t="n">
         <v>646.940771311434</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K53" t="n">
-        <v>21.56</v>
+        <v>13.78</v>
       </c>
       <c r="L53" t="n">
         <v>7.54</v>
       </c>
       <c r="M53" t="n">
-        <v>3.86</v>
+        <v>6.44</v>
       </c>
       <c r="N53" t="n">
-        <v>9.34</v>
+        <v>9.91</v>
       </c>
       <c r="O53" t="n">
         <v>-7.33</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>19.55</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45205</v>
+        <v>45208</v>
       </c>
       <c r="H54" t="n">
-        <v>830.75</v>
+        <v>790.05</v>
       </c>
       <c r="I54" t="n">
         <v>792.9914558211105</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K54" t="n">
-        <v>21.34</v>
+        <v>15.39</v>
       </c>
       <c r="L54" t="n">
         <v>16.52</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>8</v>
+      </c>
+      <c r="U54" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H55" t="n">
-        <v>797.55</v>
+        <v>818.7</v>
       </c>
       <c r="I55" t="n">
         <v>818.0947940974106</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.95</v>
+        <v>-3.63</v>
       </c>
       <c r="L55" t="n">
         <v>4.73</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.3</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H56" t="n">
-        <v>1301.3</v>
+        <v>1209.55</v>
       </c>
       <c r="I56" t="n">
         <v>1252.007788153346</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K56" t="n">
-        <v>58.95</v>
+        <v>47.74</v>
       </c>
       <c r="L56" t="n">
         <v>4.12</v>
@@ -3633,7 +4304,7 @@
         <v>1.58</v>
       </c>
       <c r="N56" t="n">
-        <v>5.76</v>
+        <v>7.05</v>
       </c>
       <c r="O56" t="n">
         <v>2.65</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>13.3</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H57" t="n">
-        <v>1341.85</v>
+        <v>1375.9</v>
       </c>
       <c r="I57" t="n">
         <v>1366.677327531158</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K57" t="n">
-        <v>-10.94</v>
+        <v>-13.75</v>
       </c>
       <c r="L57" t="n">
-        <v>12.33</v>
+        <v>14.24</v>
       </c>
       <c r="M57" t="n">
         <v>1.17</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H58" t="n">
-        <v>1287.65</v>
+        <v>1277.25</v>
       </c>
       <c r="I58" t="n">
         <v>1285.661266619063</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K58" t="n">
-        <v>-6.41</v>
+        <v>-7.17</v>
       </c>
       <c r="L58" t="n">
         <v>8.640000000000001</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.1</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45430</v>
+        <v>45433</v>
       </c>
       <c r="H59" t="n">
-        <v>1340.2</v>
+        <v>1385.5</v>
       </c>
       <c r="I59" t="n">
         <v>1365.264328625286</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.93</v>
+        <v>-8.48</v>
       </c>
       <c r="L59" t="n">
-        <v>7.01</v>
+        <v>9.52</v>
       </c>
       <c r="M59" t="n">
         <v>1.07</v>
       </c>
       <c r="N59" t="n">
-        <v>3.13</v>
+        <v>3.38</v>
       </c>
       <c r="O59" t="n">
         <v>-0.8100000000000001</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.51</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H60" t="n">
-        <v>1583.95</v>
+        <v>1248.95</v>
       </c>
       <c r="I60" t="n">
         <v>1401.402847583265</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K60" t="n">
-        <v>14.32</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>3.79</v>
+        <v>14.25</v>
       </c>
       <c r="M60" t="n">
-        <v>0.58</v>
+        <v>1.64</v>
       </c>
       <c r="N60" t="n">
-        <v>2.18</v>
+        <v>21.15</v>
       </c>
       <c r="O60" t="n">
         <v>3.38</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>32.18</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H61" t="n">
-        <v>1546.25</v>
+        <v>1569.9</v>
       </c>
       <c r="I61" t="n">
         <v>1553.285855967323</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="n">
-        <v>-23.8</v>
+        <v>-25.7</v>
       </c>
       <c r="L61" t="n">
-        <v>24.82</v>
+        <v>26.34</v>
       </c>
       <c r="M61" t="n">
         <v>2.57</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>7.24</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45517</v>
+        <v>45518</v>
       </c>
       <c r="H62" t="n">
-        <v>1483.45</v>
+        <v>1461.95</v>
       </c>
       <c r="I62" t="n">
         <v>1480.153853792034</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K62" t="n">
-        <v>-5.51</v>
+        <v>-6.88</v>
       </c>
       <c r="L62" t="n">
-        <v>7.17</v>
+        <v>7.51</v>
       </c>
       <c r="M62" t="n">
         <v>3.02</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.81</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="H63" t="n">
-        <v>1215.8</v>
+        <v>1288.65</v>
       </c>
       <c r="I63" t="n">
         <v>1270.313114563714</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K63" t="n">
-        <v>16.84</v>
+        <v>11.85</v>
       </c>
       <c r="L63" t="n">
         <v>3.77</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>5</v>
+      </c>
+      <c r="U63" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>17.65</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45666</v>
+        <v>45667</v>
       </c>
       <c r="H64" t="n">
-        <v>1132.35</v>
+        <v>1112.2</v>
       </c>
       <c r="I64" t="n">
         <v>1121.975230499703</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K64" t="n">
-        <v>-12.13</v>
+        <v>-13.69</v>
       </c>
       <c r="L64" t="n">
-        <v>12.32</v>
+        <v>14.15</v>
       </c>
       <c r="M64" t="n">
         <v>1.86</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>10.17</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45733</v>
+        <v>45734</v>
       </c>
       <c r="H65" t="n">
-        <v>1137.15</v>
+        <v>1158.8</v>
       </c>
       <c r="I65" t="n">
         <v>1155.069913258575</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.24</v>
+        <v>-4.19</v>
       </c>
       <c r="L65" t="n">
         <v>7</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.73</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="H66" t="n">
-        <v>1392.3</v>
+        <v>1372.6</v>
       </c>
       <c r="I66" t="n">
         <v>1387.197232247072</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K66" t="n">
-        <v>20.15</v>
+        <v>18.45</v>
       </c>
       <c r="L66" t="n">
         <v>10.12</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.62</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45835</v>
+        <v>45838</v>
       </c>
       <c r="H67" t="n">
-        <v>1440.2</v>
+        <v>1450.2</v>
       </c>
       <c r="I67" t="n">
         <v>1441.863127467881</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.92</v>
+        <v>-5.65</v>
       </c>
       <c r="L67" t="n">
         <v>6.13</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>7.17</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H68" t="n">
-        <v>1396.3</v>
+        <v>1376</v>
       </c>
       <c r="I68" t="n">
         <v>1385.359037357631</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.72</v>
+        <v>-5.12</v>
       </c>
       <c r="L68" t="n">
-        <v>4.15</v>
+        <v>5.29</v>
       </c>
       <c r="M68" t="n">
         <v>0.12</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.42</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H69" t="n">
-        <v>1395.2</v>
+        <v>1408.2</v>
       </c>
       <c r="I69" t="n">
         <v>1397.159841842677</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.4</v>
+        <v>-2.34</v>
       </c>
       <c r="L69" t="n">
         <v>3.42</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>5.62</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="H70" t="n">
-        <v>1487.1</v>
+        <v>1454.4</v>
       </c>
       <c r="I70" t="n">
         <v>1456.721908590898</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K70" t="n">
-        <v>5.6</v>
+        <v>3.28</v>
       </c>
       <c r="L70" t="n">
         <v>2.17</v>
@@ -4431,7 +5270,7 @@
         <v>0.68</v>
       </c>
       <c r="N70" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O70" t="n">
         <v>0.93</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>5.71</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="H71" t="n">
-        <v>1403.1</v>
+        <v>1530.8</v>
       </c>
       <c r="I71" t="n">
         <v>1472.736769582408</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K71" t="n">
-        <v>3.53</v>
+        <v>-5.25</v>
       </c>
       <c r="L71" t="n">
-        <v>2.92</v>
+        <v>5.68</v>
       </c>
       <c r="M71" t="n">
-        <v>1.98</v>
+        <v>5.28</v>
       </c>
       <c r="N71" t="n">
-        <v>4.33</v>
+        <v>9.1</v>
       </c>
       <c r="O71" t="n">
         <v>-2.2</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,28 +5387,28 @@
         <v>13.01</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H72" t="n">
-        <v>1477.5</v>
+        <v>1421.3</v>
       </c>
       <c r="I72" t="n">
         <v>1426.770898306005</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.48</v>
+        <v>-7.15</v>
       </c>
       <c r="L72" t="n">
-        <v>7.96</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M72" t="n">
-        <v>3.88</v>
+        <v>4.91</v>
       </c>
       <c r="N72" t="n">
-        <v>3.33</v>
+        <v>3.8</v>
       </c>
       <c r="O72" t="n">
         <v>9.1</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>10.6</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H73" t="n">
-        <v>1447.4</v>
+        <v>1475.3</v>
       </c>
       <c r="I73" t="n">
         <v>1462.348738558601</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.84</v>
+        <v>-3.8</v>
       </c>
       <c r="L73" t="n">
         <v>5.94</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>11.86</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H74" t="n">
-        <v>1774.7</v>
+        <v>1719.7</v>
       </c>
       <c r="I74" t="n">
         <v>1755.007197994866</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K74" t="n">
-        <v>20.29</v>
+        <v>16.57</v>
       </c>
       <c r="L74" t="n">
         <v>3.68</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="H75" t="n">
-        <v>1710</v>
+        <v>1775</v>
       </c>
       <c r="I75" t="n">
         <v>1760.477864437547</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5600000000000001</v>
+        <v>-3.22</v>
       </c>
       <c r="L75" t="n">
         <v>4.2</v>
@@ -4716,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="O75" t="n">
         <v>-3.1</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4776,6 +5687,14 @@
       <c r="Q76" t="n">
         <v>33</v>
       </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9734,7 +10653,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55.9</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="6">
@@ -9744,7 +10663,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -9754,7 +10673,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8">
@@ -9764,7 +10683,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9774,7 +10693,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -9784,7 +10703,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101.7</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="11">
@@ -9824,7 +10743,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.31</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="15">
@@ -9834,7 +10753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.24</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="16">
@@ -9844,7 +10763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.37</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="17">
@@ -9854,7 +10773,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>131.4</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="18">
@@ -9864,7 +10783,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.3</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="19">
@@ -9874,7 +10793,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.53</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="20">
@@ -9884,7 +10803,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.62</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="21">
@@ -9894,7 +10813,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24.82</v>
+        <v>26.34</v>
       </c>
     </row>
     <row r="22">
@@ -9904,7 +10823,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -9914,7 +10833,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -9924,7 +10843,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="25">
@@ -9934,7 +10853,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.57</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9944,7 +10863,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.75</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="27">
@@ -9954,7 +10873,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.53</v>
+        <v>21.15</v>
       </c>
     </row>
     <row r="28">
@@ -9964,7 +10883,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
